--- a/output/graficos_nacionales/plot_nacional_m_movinterna_a_2020.xlsx
+++ b/output/graficos_nacionales/plot_nacional_m_movinterna_a_2020.xlsx
@@ -16233,7 +16233,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Movilidad interna (CMI)</t>
+          <t>Por comunas</t>
         </is>
       </c>
     </row>

--- a/output/graficos_nacionales/plot_nacional_m_movinterna_a_2020.xlsx
+++ b/output/graficos_nacionales/plot_nacional_m_movinterna_a_2020.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="731">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="734">
   <si>
     <t xml:space="preserve">year</t>
   </si>
@@ -2173,7 +2173,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 22:22</t>
+    <t xml:space="preserve">2026-07-30 15:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2185,16 +2185,25 @@
     <t xml:space="preserve">Imagen asociada</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">plot_nacional_m_movinterna_a_2020.png</t>
   </si>
   <si>
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
+    <t xml:space="preserve">Movilidad interna (CMI)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
+    <t xml:space="preserve">Comuna (vista nacional macrozonal)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Año</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020</t>
   </si>
   <si>
     <t xml:space="preserve">variable</t>
@@ -13647,23 +13656,23 @@
         <v>723</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>722</v>
+        <v>728</v>
       </c>
     </row>
   </sheetData>
@@ -13685,21 +13694,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>15</v>
@@ -13708,7 +13717,7 @@
         <v>2020</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_nacionales/plot_nacional_m_movinterna_a_2020.xlsx
+++ b/output/graficos_nacionales/plot_nacional_m_movinterna_a_2020.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Macrozona Austral</t>
   </si>
   <si>
-    <t xml:space="preserve">value</t>
+    <t xml:space="preserve">Valor (por 1.000)</t>
   </si>
   <si>
     <t xml:space="preserve">12402</t>
@@ -601,18 +601,18 @@
     <t xml:space="preserve">Coihueco</t>
   </si>
   <si>
+    <t xml:space="preserve">6309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pumanque</t>
+  </si>
+  <si>
     <t xml:space="preserve">16102</t>
   </si>
   <si>
     <t xml:space="preserve">Bulnes</t>
   </si>
   <si>
-    <t xml:space="preserve">6309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pumanque</t>
-  </si>
-  <si>
     <t xml:space="preserve">13505</t>
   </si>
   <si>
@@ -937,18 +937,18 @@
     <t xml:space="preserve">Coinco</t>
   </si>
   <si>
+    <t xml:space="preserve">5101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valparaíso</t>
+  </si>
+  <si>
     <t xml:space="preserve">6107</t>
   </si>
   <si>
     <t xml:space="preserve">Las Cabras</t>
   </si>
   <si>
-    <t xml:space="preserve">5101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valparaíso</t>
-  </si>
-  <si>
     <t xml:space="preserve">5506</t>
   </si>
   <si>
@@ -1075,18 +1075,18 @@
     <t xml:space="preserve">San Clemente</t>
   </si>
   <si>
+    <t xml:space="preserve">5404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petorca</t>
+  </si>
+  <si>
     <t xml:space="preserve">7404</t>
   </si>
   <si>
     <t xml:space="preserve">Parral</t>
   </si>
   <si>
-    <t xml:space="preserve">5404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petorca</t>
-  </si>
-  <si>
     <t xml:space="preserve">7302</t>
   </si>
   <si>
@@ -1708,18 +1708,18 @@
     <t xml:space="preserve">Río Bueno</t>
   </si>
   <si>
+    <t xml:space="preserve">8103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chiguayante</t>
+  </si>
+  <si>
     <t xml:space="preserve">14105</t>
   </si>
   <si>
     <t xml:space="preserve">Máfil</t>
   </si>
   <si>
-    <t xml:space="preserve">8103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chiguayante</t>
-  </si>
-  <si>
     <t xml:space="preserve">8310</t>
   </si>
   <si>
@@ -2173,7 +2173,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 15:30</t>
+    <t xml:space="preserve">2026-09-08 10:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2590,9 +2590,9 @@
     <col min="5" max="5" width="22.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="14.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="19.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="12.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="19.71" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="10.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="14.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="19.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5416,10 +5416,10 @@
         <v>2020</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>194</v>
@@ -5448,10 +5448,10 @@
         <v>2020</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>196</v>
@@ -7208,10 +7208,10 @@
         <v>2020</v>
       </c>
       <c r="B145" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>306</v>
@@ -7240,10 +7240,10 @@
         <v>2020</v>
       </c>
       <c r="B146" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>308</v>
@@ -7944,10 +7944,10 @@
         <v>2020</v>
       </c>
       <c r="B168" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>352</v>
@@ -7976,10 +7976,10 @@
         <v>2020</v>
       </c>
       <c r="B169" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="D169" s="2" t="s">
         <v>354</v>
@@ -11144,10 +11144,10 @@
         <v>2020</v>
       </c>
       <c r="B268" s="2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="D268" s="2" t="s">
         <v>563</v>
@@ -11176,10 +11176,10 @@
         <v>2020</v>
       </c>
       <c r="B269" s="2" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>512</v>
+        <v>521</v>
       </c>
       <c r="D269" s="2" t="s">
         <v>565</v>
@@ -13687,7 +13687,7 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="16.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="10.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="19.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="10.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="13.71" hidden="0" customWidth="1"/>
   </cols>
